--- a/bs.xlsx
+++ b/bs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bancada\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guilherme.oliveira\Downloads\Prime\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C456ABC2-F0A1-4FAC-86C2-745B17ADD20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328A8606-2BF5-4A6A-ADA7-7FE94DFE7216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{25376A1C-37B5-4157-9E46-F499AAEA1628}"/>
+    <workbookView xWindow="-30828" yWindow="0" windowWidth="30936" windowHeight="16776" xr2:uid="{25376A1C-37B5-4157-9E46-F499AAEA1628}"/>
   </bookViews>
   <sheets>
     <sheet name="bs" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="95">
   <si>
     <t>id</t>
   </si>
@@ -47,40 +47,283 @@
     <t>url</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(1).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(2).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(3).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(4).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(5).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(6).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(7).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(8).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(9).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(10).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(11).png</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(12).png</t>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/1.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/2.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/3.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/4.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/5.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/6.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/7.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/8.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/9.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/10.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/11.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/12.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/13.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/14.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/15.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/16.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/17.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/18.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/19.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/20.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/21.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/22.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/23.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/24.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/25.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/26.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/27.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/28.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/29.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/30.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/31.png</t>
+  </si>
+  <si>
+    <t>F3F1757D</t>
+  </si>
+  <si>
+    <t>F3F2146D</t>
+  </si>
+  <si>
+    <t>F3F2A07D</t>
+  </si>
+  <si>
+    <t>F3F15F1D</t>
+  </si>
+  <si>
+    <t>9F2F88DA</t>
+  </si>
+  <si>
+    <t>F3F27E9D</t>
+  </si>
+  <si>
+    <t>9DF2756A</t>
+  </si>
+  <si>
+    <t>9F2FFF6A</t>
+  </si>
+  <si>
+    <t>F3F1845D</t>
+  </si>
+  <si>
+    <t>F3F39A9D</t>
+  </si>
+  <si>
+    <t>9F2F8E4A</t>
+  </si>
+  <si>
+    <t>3A21EBE9</t>
+  </si>
+  <si>
+    <t>9DF03BBA</t>
+  </si>
+  <si>
+    <t>9F2E5B2A</t>
+  </si>
+  <si>
+    <t>F3F24F1D</t>
+  </si>
+  <si>
+    <t>F3F3384D</t>
+  </si>
+  <si>
+    <t>F3F0B8BD</t>
+  </si>
+  <si>
+    <t>9DEDB31A</t>
+  </si>
+  <si>
+    <t>F3F36DBD</t>
+  </si>
+  <si>
+    <t>F3F1FD7D</t>
+  </si>
+  <si>
+    <t>9DF0263A</t>
+  </si>
+  <si>
+    <t>F3F3B43D</t>
+  </si>
+  <si>
+    <t>9DEB9EAA</t>
+  </si>
+  <si>
+    <t>F3F139AD</t>
+  </si>
+  <si>
+    <t>F3F4413D</t>
+  </si>
+  <si>
+    <t>9DF0AC3A</t>
+  </si>
+  <si>
+    <t>F3F2356D</t>
+  </si>
+  <si>
+    <t>F3F2077D</t>
+  </si>
+  <si>
+    <t>F3F0E76D</t>
+  </si>
+  <si>
+    <t>F3F3E3DD</t>
+  </si>
+  <si>
+    <t>F3F0EF1D</t>
+  </si>
+  <si>
+    <t>000043BB</t>
+  </si>
+  <si>
+    <t>00004AEA</t>
+  </si>
+  <si>
+    <t>00004771</t>
+  </si>
+  <si>
+    <t>00004794</t>
+  </si>
+  <si>
+    <t>00004EB6</t>
+  </si>
+  <si>
+    <t>000048F4</t>
+  </si>
+  <si>
+    <t>00003863</t>
+  </si>
+  <si>
+    <t>00004D97</t>
+  </si>
+  <si>
+    <t>0000438B</t>
+  </si>
+  <si>
+    <t>00004663</t>
+  </si>
+  <si>
+    <t>00004F59</t>
+  </si>
+  <si>
+    <t>00004F5E</t>
+  </si>
+  <si>
+    <t>0000364B</t>
+  </si>
+  <si>
+    <t>00004A5B</t>
+  </si>
+  <si>
+    <t>000047E2</t>
+  </si>
+  <si>
+    <t>000048C2</t>
+  </si>
+  <si>
+    <t>00004808</t>
+  </si>
+  <si>
+    <t>00004CFA</t>
+  </si>
+  <si>
+    <t>00004BD3</t>
+  </si>
+  <si>
+    <t>00004AD0</t>
+  </si>
+  <si>
+    <t>00004D64</t>
+  </si>
+  <si>
+    <t>00004B6A</t>
+  </si>
+  <si>
+    <t>00004C9C</t>
+  </si>
+  <si>
+    <t>00003D0E</t>
+  </si>
+  <si>
+    <t>00003862</t>
+  </si>
+  <si>
+    <t>00004CD5</t>
+  </si>
+  <si>
+    <t>0000498A</t>
+  </si>
+  <si>
+    <t>0000269B</t>
+  </si>
+  <si>
+    <t>00004A75</t>
+  </si>
+  <si>
+    <t>000043A9</t>
+  </si>
+  <si>
+    <t>00003D5E</t>
   </si>
 </sst>
 </file>
@@ -133,7 +376,68 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -463,14 +767,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B7CB59-4036-435B-849D-7966C961046C}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B63"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="90.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -478,105 +782,524 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>81</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>83</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>87</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>88</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>89</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>90</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>91</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>92</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>93</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>94</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A33:A38">
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A33:A52">
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53:A59">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53:A63">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{2F87C273-A2F2-42FE-B26B-6814931C6678}"/>
+    <hyperlink ref="B2" r:id="rId1" display="https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(1).png" xr:uid="{2F87C273-A2F2-42FE-B26B-6814931C6678}"/>
+    <hyperlink ref="B3:B13" r:id="rId2" display="https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(1).png" xr:uid="{5FC63469-0029-4102-BF40-9C4731AADBAF}"/>
+    <hyperlink ref="B14:B34" r:id="rId3" display="https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(1).png" xr:uid="{5CCB3951-A26E-4856-9A2B-9E7962C74C57}"/>
+    <hyperlink ref="B33" r:id="rId4" display="https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(1).png" xr:uid="{D6F061FF-5CA5-46A6-9E8C-06EA484DCA44}"/>
+    <hyperlink ref="B34:B44" r:id="rId5" display="https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(1).png" xr:uid="{A4E5C6C1-F98D-4EC8-8F53-8B67617B3338}"/>
+    <hyperlink ref="B45:B63" r:id="rId6" display="https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(1).png" xr:uid="{62757313-68AD-4564-854E-93589D0A5222}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/bs.xlsx
+++ b/bs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guilherme.oliveira\Downloads\Prime\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25ED804B-9109-4F89-8CD7-E16F680EB72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187A017B-DC04-449A-8616-2FFB88023922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30828" yWindow="0" windowWidth="30936" windowHeight="16776" xr2:uid="{25376A1C-37B5-4157-9E46-F499AAEA1628}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="97">
   <si>
     <t>id</t>
   </si>
@@ -231,6 +231,105 @@
   </si>
   <si>
     <t>F3F0EF1D</t>
+  </si>
+  <si>
+    <t>000043BB</t>
+  </si>
+  <si>
+    <t>00004AEA</t>
+  </si>
+  <si>
+    <t>00004771</t>
+  </si>
+  <si>
+    <t>00004794</t>
+  </si>
+  <si>
+    <t>00004EB6</t>
+  </si>
+  <si>
+    <t>000048F4</t>
+  </si>
+  <si>
+    <t>00003863</t>
+  </si>
+  <si>
+    <t>00004D97</t>
+  </si>
+  <si>
+    <t>0000438B</t>
+  </si>
+  <si>
+    <t>00004663</t>
+  </si>
+  <si>
+    <t>00004F59</t>
+  </si>
+  <si>
+    <t>00004F5E</t>
+  </si>
+  <si>
+    <t>0000364B</t>
+  </si>
+  <si>
+    <t>00004A5B</t>
+  </si>
+  <si>
+    <t>000047E2</t>
+  </si>
+  <si>
+    <t>000048C2</t>
+  </si>
+  <si>
+    <t>00004808</t>
+  </si>
+  <si>
+    <t>00004CFA</t>
+  </si>
+  <si>
+    <t>00004BD3</t>
+  </si>
+  <si>
+    <t>00004AD0</t>
+  </si>
+  <si>
+    <t>00004D64</t>
+  </si>
+  <si>
+    <t>00004B6A</t>
+  </si>
+  <si>
+    <t>00004C9C</t>
+  </si>
+  <si>
+    <t>00003D0E</t>
+  </si>
+  <si>
+    <t>00003862</t>
+  </si>
+  <si>
+    <t>00004CD5</t>
+  </si>
+  <si>
+    <t>0000498A</t>
+  </si>
+  <si>
+    <t>0000269B</t>
+  </si>
+  <si>
+    <t>00004A75</t>
+  </si>
+  <si>
+    <t>000043A9</t>
+  </si>
+  <si>
+    <t>00003D5E</t>
+  </si>
+  <si>
+    <t>3A212A79</t>
+  </si>
+  <si>
+    <t>3A21B049</t>
   </si>
 </sst>
 </file>
@@ -674,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B7CB59-4036-435B-849D-7966C961046C}">
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.4609375" bestFit="1" customWidth="1"/>
@@ -938,250 +1037,266 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A33">
-        <v>17339</v>
+      <c r="A33" t="s">
+        <v>64</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A34">
-        <v>19178</v>
+      <c r="A34" t="s">
+        <v>65</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35">
-        <v>18289</v>
+      <c r="A35" t="s">
+        <v>66</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36">
-        <v>18324</v>
+      <c r="A36" t="s">
+        <v>67</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37">
-        <v>20150</v>
+      <c r="A37" t="s">
+        <v>68</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38">
-        <v>18676</v>
+      <c r="A38" t="s">
+        <v>69</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A39">
-        <v>14435</v>
+      <c r="A39" t="s">
+        <v>70</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A40">
-        <v>19863</v>
+      <c r="A40" t="s">
+        <v>71</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A41">
-        <v>17291</v>
+      <c r="A41" t="s">
+        <v>72</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A42">
-        <v>18019</v>
+      <c r="A42" t="s">
+        <v>73</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A43">
-        <v>20313</v>
+      <c r="A43" t="s">
+        <v>74</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A44">
-        <v>20318</v>
+      <c r="A44" t="s">
+        <v>75</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A45">
-        <v>13899</v>
+      <c r="A45" t="s">
+        <v>76</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A46">
-        <v>19035</v>
+      <c r="A46" t="s">
+        <v>77</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A47">
-        <v>18402</v>
+      <c r="A47" t="s">
+        <v>78</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A48">
-        <v>18626</v>
+      <c r="A48" t="s">
+        <v>79</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A49">
-        <v>18440</v>
+      <c r="A49" t="s">
+        <v>80</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A50">
-        <v>19706</v>
+      <c r="A50" t="s">
+        <v>81</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A51">
-        <v>19411</v>
+      <c r="A51" t="s">
+        <v>82</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A52">
-        <v>19152</v>
+      <c r="A52" t="s">
+        <v>83</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A53">
-        <v>19812</v>
+      <c r="A53" t="s">
+        <v>84</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A54">
-        <v>19306</v>
+      <c r="A54" t="s">
+        <v>85</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A55">
-        <v>19612</v>
+      <c r="A55" t="s">
+        <v>86</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A56">
-        <v>15630</v>
+      <c r="A56" t="s">
+        <v>87</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A57">
-        <v>14434</v>
+      <c r="A57" t="s">
+        <v>88</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A58">
-        <v>19669</v>
+      <c r="A58" t="s">
+        <v>89</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A59">
-        <v>18826</v>
+      <c r="A59" t="s">
+        <v>90</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A60">
-        <v>9883</v>
+      <c r="A60" t="s">
+        <v>91</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A61">
-        <v>19061</v>
+      <c r="A61" t="s">
+        <v>92</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A62">
-        <v>17321</v>
+      <c r="A62" t="s">
+        <v>93</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A63">
-        <v>15710</v>
+      <c r="A63" t="s">
+        <v>94</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>95</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1208,6 +1323,7 @@
     <hyperlink ref="B34:B44" r:id="rId5" display="https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(1).png" xr:uid="{A4E5C6C1-F98D-4EC8-8F53-8B67617B3338}"/>
     <hyperlink ref="B45:B63" r:id="rId6" display="https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(1).png" xr:uid="{62757313-68AD-4564-854E-93589D0A5222}"/>
     <hyperlink ref="B10" r:id="rId7" xr:uid="{F4EC99EF-78C6-47E1-B88B-97887632F826}"/>
+    <hyperlink ref="B64:B65" r:id="rId8" display="https://raw.githubusercontent.com/GuilhermeJobs/temp_img/refs/heads/main/Img/img%20(1).png" xr:uid="{2AF34593-B205-473F-BB48-D038E41D5BD5}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
